--- a/data/trans_dic/P19C08-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P19C08-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por selladores, aplicación de fluor</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por selladores, aplicación de fluor (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,22 +717,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,32</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,71</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,16</t>
+          <t>0,0; 4,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,22 +742,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,66</t>
+          <t>0,26; 2,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,66</t>
+          <t>0,0; 3,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,93</t>
+          <t>0,0; 0,79</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 3,17</t>
+          <t>0,37; 3,67</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,39</t>
+          <t>0,0; 1,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,28</t>
+          <t>0,28; 2,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,4</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,26</t>
+          <t>0,0; 0,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,99</t>
+          <t>0,15; 2,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,08</t>
+          <t>0,34; 2,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,16</t>
+          <t>0,0; 1,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,24</t>
+          <t>0,25; 1,27</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,6</t>
+          <t>0,42; 1,76</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,64</t>
+          <t>0,0; 0,58</t>
         </is>
       </c>
     </row>
@@ -1002,57 +1002,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,1</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,02</t>
+          <t>0,0; 0,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,79</t>
+          <t>0,19; 1,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,25</t>
+          <t>0,0; 1,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,76</t>
+          <t>0,3; 1,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,42</t>
+          <t>0,25; 1,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,84</t>
+          <t>0,09; 0,88</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,17</t>
+          <t>0,3; 1,22</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,9</t>
+          <t>0,09; 1,0</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,31</t>
+          <t>0,3; 1,25</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,6</t>
+          <t>0,18; 2,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,66</t>
+          <t>0,0; 0,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,53</t>
+          <t>0,0; 1,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,97</t>
+          <t>0,18; 2,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,8</t>
+          <t>0,09; 0,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,1</t>
+          <t>0,11; 1,21</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,66</t>
+          <t>0,27; 1,65</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,51</t>
+          <t>0,07; 0,55</t>
         </is>
       </c>
     </row>
@@ -1277,32 +1277,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,46</t>
+          <t>0,0; 1,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,05</t>
+          <t>0,0; 1,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,45</t>
+          <t>0,15; 1,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,17</t>
+          <t>0,0; 2,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1312,27 +1312,27 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,69</t>
+          <t>0,03; 0,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,01</t>
+          <t>0,0; 1,17</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,7</t>
+          <t>0,0; 0,83</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,24</t>
+          <t>0,13; 1,16</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,9</t>
+          <t>0,11; 0,81</t>
         </is>
       </c>
     </row>
@@ -1417,37 +1417,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,75</t>
+          <t>0,0; 3,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>0,0; 1,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>0,0; 2,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,23</t>
+          <t>0,13; 1,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,81</t>
+          <t>0,0; 2,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,65</t>
+          <t>0,2; 1,64</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,9</t>
+          <t>0,0; 0,89</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,78</t>
+          <t>0,1; 0,75</t>
         </is>
       </c>
     </row>
@@ -1557,37 +1557,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,08; 4,03</t>
+          <t>0,44; 4,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,75</t>
+          <t>0,0; 1,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,92</t>
+          <t>0,0; 3,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,03</t>
+          <t>0,0; 3,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1597,22 +1597,22 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,45</t>
+          <t>0,0; 2,13</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,64</t>
+          <t>0,17; 1,77</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,31</t>
+          <t>0,0; 1,98</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,86</t>
+          <t>0,09; 0,9</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,64</t>
+          <t>0,15; 0,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,99</t>
+          <t>0,36; 1,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,36</t>
+          <t>0,04; 0,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,85</t>
+          <t>0,25; 0,83</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,89</t>
+          <t>0,29; 0,9</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,96</t>
+          <t>0,37; 0,94</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,43</t>
+          <t>0,08; 0,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,61</t>
+          <t>0,23; 0,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,66</t>
+          <t>0,29; 0,68</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,85</t>
+          <t>0,43; 0,86</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,35</t>
+          <t>0,08; 0,34</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,61</t>
+          <t>0,28; 0,63</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por selladores, aplicación de fluor</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por selladores, aplicación de fluor (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4758</t>
+          <t>0; 5471</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6471</t>
+          <t>0; 6604</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2040</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 19783</t>
+          <t>0; 18983</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4925</t>
+          <t>0; 4943</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1081; 9863</t>
+          <t>979; 10168</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 1877</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 11114</t>
+          <t>0; 9330</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 6809</t>
+          <t>0; 5848</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2284; 12389</t>
+          <t>2247; 12413</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 1958</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1783; 21773</t>
+          <t>2549; 25222</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>931; 8001</t>
+          <t>0; 8589</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1264; 13588</t>
+          <t>1671; 13704</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1989</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 1027</t>
+          <t>0; 967</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>808; 10887</t>
+          <t>803; 11325</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1912; 11632</t>
+          <t>1922; 11980</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 1866</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5782</t>
+          <t>0; 4992</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2492; 13894</t>
+          <t>2832; 14254</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4705; 18432</t>
+          <t>4823; 20323</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 1928</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 5792</t>
+          <t>0; 5254</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5355</t>
+          <t>0; 5338</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 6434</t>
+          <t>0; 6997</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5713</t>
+          <t>0; 4356</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1008; 9380</t>
+          <t>993; 9548</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 7573</t>
+          <t>0; 6494</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1922; 11580</t>
+          <t>1947; 11704</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 8727</t>
+          <t>0; 9155</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1559; 7547</t>
+          <t>1349; 7503</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1025; 9339</t>
+          <t>1017; 9759</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3792; 14564</t>
+          <t>3792; 15229</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1028; 10217</t>
+          <t>1019; 11321</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3371; 13861</t>
+          <t>3175; 13205</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5720</t>
+          <t>0; 6376</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1003; 14114</t>
+          <t>1001; 13723</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2120</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 5721</t>
+          <t>0; 5362</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 6705</t>
+          <t>0; 6895</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1041; 11117</t>
+          <t>1041; 12478</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 2059</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>646; 5627</t>
+          <t>662; 6354</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>924; 9289</t>
+          <t>927; 10240</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3119; 18399</t>
+          <t>3039; 18256</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 2091</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1046; 8006</t>
+          <t>1020; 8570</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1887</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5276</t>
+          <t>0; 5301</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 7594</t>
+          <t>0; 6735</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>823; 7942</t>
+          <t>844; 8357</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 6936</t>
+          <t>0; 6905</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 2119</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4858</t>
+          <t>0; 4875</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>160; 3680</t>
+          <t>161; 3343</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 5946</t>
+          <t>0; 6946</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 5242</t>
+          <t>0; 6242</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>969; 9493</t>
+          <t>965; 8872</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1196; 9717</t>
+          <t>1235; 8778</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5857</t>
+          <t>0; 6726</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6015</t>
+          <t>0; 5167</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4601</t>
+          <t>0; 5229</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>473; 4434</t>
+          <t>476; 4593</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 6929</t>
+          <t>0; 5823</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 1976</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 2036</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 5012</t>
+          <t>0; 5028</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>699; 7569</t>
+          <t>904; 7523</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 5020</t>
+          <t>0; 4978</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 4544</t>
+          <t>0; 4537</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1049; 7497</t>
+          <t>996; 7204</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 1856</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>145; 7445</t>
+          <t>809; 8081</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 1603</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 4815</t>
+          <t>0; 4114</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 8170</t>
+          <t>0; 7065</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 2118</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 9182</t>
+          <t>0; 8242</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 3221</t>
+          <t>0; 3223</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 8214</t>
+          <t>0; 7136</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>819; 7969</t>
+          <t>814; 8608</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 8654</t>
+          <t>0; 7417</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>597; 5850</t>
+          <t>599; 6173</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3726; 15823</t>
+          <t>3733; 14941</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>9985; 28863</t>
+          <t>10441; 29281</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>915; 9708</t>
+          <t>1038; 10544</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7900; 28637</t>
+          <t>8224; 27953</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>7794; 24415</t>
+          <t>7936; 24589</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11232; 30227</t>
+          <t>11582; 29405</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2128; 12298</t>
+          <t>2214; 13015</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>7857; 21978</t>
+          <t>8204; 22048</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>14889; 34083</t>
+          <t>15066; 35260</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>25791; 51555</t>
+          <t>25996; 51859</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4368; 19251</t>
+          <t>4256; 18797</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>19151; 42190</t>
+          <t>19700; 43624</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C08-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P19C08-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>0,0; 1,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,17 +732,17 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,95</t>
+          <t>0,0; 5,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,31</t>
+          <t>0,0; 1,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,74</t>
+          <t>0,26; 2,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -752,17 +752,17 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,07</t>
+          <t>0,0; 3,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,79</t>
+          <t>0,0; 0,8</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,65</t>
+          <t>0,28; 1,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,67</t>
+          <t>0,36; 2,66</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,49</t>
+          <t>0,16; 1,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,29</t>
+          <t>0,26; 2,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,17 +872,17 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,24</t>
+          <t>0,0; 2,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,07</t>
+          <t>0,15; 1,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,15</t>
+          <t>0,35; 2,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,17 +892,17 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,0</t>
+          <t>0,0; 0,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,27</t>
+          <t>0,23; 1,19</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,76</t>
+          <t>0,41; 1,51</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,58</t>
+          <t>0,0; 1,76</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,06</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,78</t>
+          <t>0,0; 0,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,82</t>
+          <t>0,18; 1,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,08</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,77</t>
+          <t>0,29; 1,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,6</t>
+          <t>0,0; 1,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,41</t>
+          <t>0,29; 1,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,88</t>
+          <t>0,09; 0,96</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,22</t>
+          <t>0,3; 1,16</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,0</t>
+          <t>0,09; 0,86</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,25</t>
+          <t>0,3; 1,23</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,26%</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,58</t>
+          <t>0,0; 1,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,53</t>
+          <t>0,18; 2,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1152,17 +1152,17 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,62</t>
+          <t>0,0; 0,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,57</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,21</t>
+          <t>0,18; 2,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1172,17 +1172,17 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,91</t>
+          <t>0,1; 0,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,21</t>
+          <t>0,11; 1,03</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,65</t>
+          <t>0,28; 1,74</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,55</t>
+          <t>0,09; 0,55</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -1282,22 +1282,22 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,47</t>
+          <t>0,0; 1,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,82</t>
+          <t>0,0; 2,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,53</t>
+          <t>0,16; 1,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,16</t>
+          <t>0,0; 2,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1307,17 +1307,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,23</t>
+          <t>0,0; 1,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,63</t>
+          <t>0,11; 0,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,17</t>
+          <t>0,0; 1,34</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1327,12 +1327,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,16</t>
+          <t>0,13; 1,11</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,81</t>
+          <t>0,14; 0,87</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -1417,27 +1417,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,16</t>
+          <t>0,0; 2,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,97</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,27</t>
+          <t>0,0; 1,99</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,28</t>
+          <t>0,12; 1,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,36</t>
+          <t>0,0; 2,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,84</t>
+          <t>0,13; 1,25</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1462,17 +1462,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,89</t>
+          <t>0,0; 0,97</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,89</t>
+          <t>0,0; 1,2</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,75</t>
+          <t>0,15; 0,89</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,37</t>
+          <t>0,43; 3,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,49</t>
+          <t>0,0; 1,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,39</t>
+          <t>0,0; 3,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1587,32 +1587,32 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,62</t>
+          <t>0,0; 3,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,79</t>
+          <t>0,0; 0,92</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,13</t>
+          <t>0,0; 2,12</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,77</t>
+          <t>0,17; 1,62</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,98</t>
+          <t>0,0; 2,19</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,9</t>
+          <t>0,12; 0,87</t>
         </is>
       </c>
     </row>
@@ -1644,34 +1644,34 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
           <t>0,61%</t>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1697,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,61</t>
+          <t>0,19; 0,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,0</t>
+          <t>0,37; 1,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1712,27 +1712,27 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,83</t>
+          <t>0,3; 0,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,9</t>
+          <t>0,33; 0,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,94</t>
+          <t>0,37; 0,93</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,45</t>
+          <t>0,08; 0,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,62</t>
+          <t>0,29; 0,7</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,86</t>
+          <t>0,42; 0,86</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,63</t>
+          <t>0,34; 0,72</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4732</t>
+          <t>4359</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7619</t>
+          <t>7382</t>
         </is>
       </c>
     </row>
@@ -2068,12 +2068,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5471</t>
+          <t>0; 4745</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6604</t>
+          <t>0; 6574</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -2083,17 +2083,17 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 18983</t>
+          <t>0; 18986</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4943</t>
+          <t>0; 4962</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>979; 10168</t>
+          <t>967; 9603</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -2103,17 +2103,17 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 9330</t>
+          <t>0; 10733</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5848</t>
+          <t>0; 5876</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2247; 12413</t>
+          <t>2130; 12528</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2549; 25222</t>
+          <t>2593; 19186</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>2593</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1209</t>
+          <t>3653</t>
         </is>
       </c>
     </row>
@@ -2276,12 +2276,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 8589</t>
+          <t>922; 7473</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1671; 13704</t>
+          <t>1536; 13044</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2291,17 +2291,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 967</t>
+          <t>0; 11727</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>803; 11325</t>
+          <t>805; 9948</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1922; 11980</t>
+          <t>1961; 11825</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2311,17 +2311,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4992</t>
+          <t>0; 4339</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2832; 14254</t>
+          <t>2627; 13362</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4823; 20323</t>
+          <t>4731; 17482</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 5254</t>
+          <t>0; 16318</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3380</t>
+          <t>3553</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3578</t>
+          <t>4444</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6958</t>
+          <t>7997</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5338</t>
+          <t>0; 5969</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 6997</t>
+          <t>0; 6101</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4356</t>
+          <t>0; 5220</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>993; 9548</t>
+          <t>1102; 9645</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6494</t>
+          <t>0; 7631</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1947; 11704</t>
+          <t>1924; 11640</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 9155</t>
+          <t>0; 8740</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1349; 7503</t>
+          <t>1736; 9421</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1017; 9759</t>
+          <t>1015; 10626</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3792; 15229</t>
+          <t>3760; 14482</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1019; 11321</t>
+          <t>1010; 9782</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3175; 13205</t>
+          <t>3591; 14922</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1121</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2523</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3329</t>
+          <t>3644</t>
         </is>
       </c>
     </row>
@@ -2692,12 +2692,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6376</t>
+          <t>0; 6009</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1001; 13723</t>
+          <t>1003; 14190</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2707,17 +2707,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 5362</t>
+          <t>0; 5052</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 6895</t>
+          <t>0; 6847</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1041; 12478</t>
+          <t>1039; 11410</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2727,17 +2727,17 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>662; 6354</t>
+          <t>706; 6122</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>927; 10240</t>
+          <t>916; 8733</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3039; 18256</t>
+          <t>3085; 19230</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1020; 8570</t>
+          <t>1310; 7754</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2771</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3697</t>
+          <t>5090</t>
         </is>
       </c>
     </row>
@@ -2905,22 +2905,22 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5301</t>
+          <t>0; 4619</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 6735</t>
+          <t>0; 7665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>844; 8357</t>
+          <t>926; 8614</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 6905</t>
+          <t>0; 7035</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2930,32 +2930,32 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4875</t>
+          <t>0; 4424</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>161; 3343</t>
+          <t>669; 5440</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 6946</t>
+          <t>0; 7906</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 6242</t>
+          <t>0; 6268</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>965; 8872</t>
+          <t>967; 8542</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1235; 8778</t>
+          <t>1700; 10388</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1628</t>
+          <t>1772</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1662</t>
+          <t>1799</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3290</t>
+          <t>3572</t>
         </is>
       </c>
     </row>
@@ -3108,27 +3108,27 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6726</t>
+          <t>0; 5736</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5167</t>
+          <t>0; 5033</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5229</t>
+          <t>0; 4576</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>476; 4593</t>
+          <t>496; 5240</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 5823</t>
+          <t>0; 7174</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -3143,27 +3143,27 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 5028</t>
+          <t>574; 5368</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>904; 7523</t>
+          <t>904; 7547</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 4978</t>
+          <t>0; 5447</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 4537</t>
+          <t>0; 6075</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>996; 7204</t>
+          <t>1234; 7362</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2729</t>
         </is>
       </c>
     </row>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>809; 8081</t>
+          <t>789; 7181</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 4114</t>
+          <t>0; 5945</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 7065</t>
+          <t>0; 7069</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3346,32 +3346,32 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 8242</t>
+          <t>0; 8468</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 3223</t>
+          <t>0; 4119</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 7136</t>
+          <t>0; 7088</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>814; 8608</t>
+          <t>811; 7916</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 7417</t>
+          <t>0; 8204</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>599; 6173</t>
+          <t>886; 6477</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14985</t>
+          <t>17992</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>13529</t>
+          <t>16076</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>28514</t>
+          <t>34067</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3733; 14941</t>
+          <t>4592; 16673</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>10441; 29281</t>
+          <t>10838; 29661</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1038; 10544</t>
+          <t>1024; 10562</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8224; 27953</t>
+          <t>10283; 31836</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>7936; 24589</t>
+          <t>8932; 23902</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11582; 29405</t>
+          <t>11713; 29348</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2214; 13015</t>
+          <t>2218; 14876</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>8204; 22048</t>
+          <t>10417; 25346</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>15066; 35260</t>
+          <t>15000; 35213</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>25996; 51859</t>
+          <t>25516; 51921</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4256; 18797</t>
+          <t>4390; 18688</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>19700; 43624</t>
+          <t>23977; 50449</t>
         </is>
       </c>
     </row>
